--- a/apiHirams/resources/templates/ChequeTemplate.xlsx
+++ b/apiHirams/resources/templates/ChequeTemplate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My Files\Program\hirams\apiHirams\resources\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3DEB14B-E8F1-498C-A37C-49DA50DA5504}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{715C5AB9-D518-47CA-8584-E0D46DAF8B12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4DA2E332-4960-40BF-8538-CD4AA7680CA7}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="6">
   <si>
     <t xml:space="preserve"> </t>
   </si>
@@ -49,15 +49,25 @@
   <si>
     <t>AMOUNT TO WORD</t>
   </si>
+  <si>
+    <t>0  9</t>
+  </si>
+  <si>
+    <t>2  8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  2  0   2  6</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -113,14 +123,19 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <name val="Segoe UI Historic"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="13"/>
-      <name val="OCR A Extended"/>
-      <family val="3"/>
+      <name val="Segoe UI Historic"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="Calibri"/>
+      <name val="Segoe UI Historic"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -145,7 +160,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -154,20 +169,22 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="43" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -513,11 +530,11 @@
     <col min="1" max="1" width="9" style="1" customWidth="1"/>
     <col min="2" max="5" width="8.88671875" style="1"/>
     <col min="6" max="6" width="8.6640625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="8.88671875" style="1"/>
-    <col min="8" max="8" width="8.33203125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="5.44140625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="6.6640625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="8.88671875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.88671875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="6.33203125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="5" style="1" customWidth="1"/>
+    <col min="10" max="10" width="4.5546875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="3.21875" style="1" customWidth="1"/>
     <col min="12" max="14" width="8.88671875" style="1"/>
     <col min="15" max="15" width="12.6640625" style="2" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="11.5546875" style="2" bestFit="1" customWidth="1"/>
@@ -559,7 +576,7 @@
       <c r="N18" s="1"/>
     </row>
     <row r="19" spans="1:15" ht="9.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="20" spans="1:15" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" s="2" customFormat="1" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
@@ -574,23 +591,29 @@
       <c r="M20" s="1"/>
       <c r="N20" s="1"/>
     </row>
-    <row r="21" spans="1:15" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" s="2" customFormat="1" ht="19.8" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A21" s="4"/>
-      <c r="B21" s="1"/>
+      <c r="B21" s="9"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
-      <c r="I21" s="8"/>
-      <c r="J21" s="8"/>
-      <c r="K21" s="9"/>
-      <c r="L21" s="9"/>
-      <c r="M21" s="5"/>
+      <c r="H21" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="I21" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="J21" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="K21" s="13"/>
+      <c r="L21" s="13"/>
+      <c r="M21" s="8"/>
       <c r="N21" s="1"/>
     </row>
-    <row r="22" spans="1:15" s="2" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:15" s="2" customFormat="1" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="4"/>
       <c r="B22" s="10" t="s">
         <v>1</v>
@@ -601,11 +624,11 @@
       <c r="F22" s="10"/>
       <c r="G22" s="10"/>
       <c r="H22" s="10"/>
-      <c r="I22" s="12">
-        <v>0</v>
-      </c>
-      <c r="J22" s="12"/>
-      <c r="K22" s="12"/>
+      <c r="I22" s="14">
+        <v>19354.55</v>
+      </c>
+      <c r="J22" s="14"/>
+      <c r="K22" s="14"/>
       <c r="L22" s="1"/>
       <c r="M22" s="5"/>
       <c r="N22" s="1"/>
@@ -614,7 +637,7 @@
       <c r="A23" s="4"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
+      <c r="D23" s="9"/>
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
@@ -719,10 +742,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="K21:L21"/>
     <mergeCell ref="I22:K22"/>
     <mergeCell ref="B22:H22"/>
     <mergeCell ref="B24:L24"/>
+    <mergeCell ref="J21:L21"/>
   </mergeCells>
   <pageMargins left="0.41" right="0.7" top="1.73" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" horizontalDpi="180" verticalDpi="180" r:id="rId1"/>
